--- a/artfynd/A 36088-2024 artfynd.xlsx
+++ b/artfynd/A 36088-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746609</v>
+        <v>122746619</v>
       </c>
       <c r="B3" t="n">
-        <v>89991</v>
+        <v>78498</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573916</v>
+        <v>573913</v>
       </c>
       <c r="R3" t="n">
-        <v>7104883</v>
+        <v>7104833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746619</v>
+        <v>122746609</v>
       </c>
       <c r="B4" t="n">
-        <v>78498</v>
+        <v>89991</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573913</v>
+        <v>573916</v>
       </c>
       <c r="R4" t="n">
-        <v>7104833</v>
+        <v>7104883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36088-2024 artfynd.xlsx
+++ b/artfynd/A 36088-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122746611</v>
       </c>
       <c r="B2" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746619</v>
+        <v>122746609</v>
       </c>
       <c r="B3" t="n">
-        <v>78498</v>
+        <v>89995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573913</v>
+        <v>573916</v>
       </c>
       <c r="R3" t="n">
-        <v>7104833</v>
+        <v>7104883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746609</v>
+        <v>122746619</v>
       </c>
       <c r="B4" t="n">
-        <v>89991</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573916</v>
+        <v>573913</v>
       </c>
       <c r="R4" t="n">
-        <v>7104883</v>
+        <v>7104833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36088-2024 artfynd.xlsx
+++ b/artfynd/A 36088-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746611</v>
+        <v>122746609</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>89995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573880</v>
+        <v>573916</v>
       </c>
       <c r="R2" t="n">
-        <v>7104956</v>
+        <v>7104883</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746609</v>
+        <v>122746619</v>
       </c>
       <c r="B3" t="n">
-        <v>89995</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573916</v>
+        <v>573913</v>
       </c>
       <c r="R3" t="n">
-        <v>7104883</v>
+        <v>7104833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746619</v>
+        <v>122746611</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573913</v>
+        <v>573880</v>
       </c>
       <c r="R4" t="n">
-        <v>7104833</v>
+        <v>7104956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36088-2024 artfynd.xlsx
+++ b/artfynd/A 36088-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746619</v>
+        <v>122746611</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573913</v>
+        <v>573880</v>
       </c>
       <c r="R3" t="n">
-        <v>7104833</v>
+        <v>7104956</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746611</v>
+        <v>122746619</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573880</v>
+        <v>573913</v>
       </c>
       <c r="R4" t="n">
-        <v>7104956</v>
+        <v>7104833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36088-2024 artfynd.xlsx
+++ b/artfynd/A 36088-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746609</v>
+        <v>122746611</v>
       </c>
       <c r="B2" t="n">
-        <v>89995</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573916</v>
+        <v>573880</v>
       </c>
       <c r="R2" t="n">
-        <v>7104883</v>
+        <v>7104956</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746611</v>
+        <v>122746609</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>89995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573880</v>
+        <v>573916</v>
       </c>
       <c r="R3" t="n">
-        <v>7104956</v>
+        <v>7104883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 36088-2024 artfynd.xlsx
+++ b/artfynd/A 36088-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746609</v>
+        <v>122746611</v>
       </c>
       <c r="B2" t="n">
-        <v>89995</v>
+        <v>79850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573916</v>
+        <v>573880</v>
       </c>
       <c r="R2" t="n">
-        <v>7104883</v>
+        <v>7104956</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746619</v>
+        <v>122746609</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>89998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573913</v>
+        <v>573916</v>
       </c>
       <c r="R3" t="n">
-        <v>7104833</v>
+        <v>7104883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746611</v>
+        <v>122746619</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78505</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573880</v>
+        <v>573913</v>
       </c>
       <c r="R4" t="n">
-        <v>7104956</v>
+        <v>7104833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36088-2024 artfynd.xlsx
+++ b/artfynd/A 36088-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746611</v>
+        <v>122746609</v>
       </c>
       <c r="B2" t="n">
-        <v>79850</v>
+        <v>90000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573880</v>
+        <v>573916</v>
       </c>
       <c r="R2" t="n">
-        <v>7104956</v>
+        <v>7104883</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746609</v>
+        <v>122746619</v>
       </c>
       <c r="B3" t="n">
-        <v>89998</v>
+        <v>78507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573916</v>
+        <v>573913</v>
       </c>
       <c r="R3" t="n">
-        <v>7104883</v>
+        <v>7104833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746619</v>
+        <v>122746611</v>
       </c>
       <c r="B4" t="n">
-        <v>78505</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573913</v>
+        <v>573880</v>
       </c>
       <c r="R4" t="n">
-        <v>7104833</v>
+        <v>7104956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
